--- a/BCE7518_COMPUTER_VISION.xlsx
+++ b/BCE7518_COMPUTER_VISION.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fe3b244c9c926f8f/Desktop/Question Paper Generator/Updated Backend Host/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fe3b244c9c926f8f/Desktop/Question Paper Generator/exam-engine-frontend/Backend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{3F4FAFA4-41C0-497B-BE9C-2082A199B40F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFE4B6C4-0A4B-4F86-B5CB-08210A152ABD}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F4FAFA4-41C0-497B-BE9C-2082A199B40F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5760" yWindow="3360" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Question Paper - General Inform" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="210">
   <si>
     <t>Branch</t>
   </si>
@@ -1561,6 +1561,12 @@
 iii. Neat labelled diagrams must be drawn wherever necessary.
 iv. Figure to right indicates full marks.
 v. Use of a non-programmable calculator is allowed.</t>
+  </si>
+  <si>
+    <t>Set</t>
+  </si>
+  <si>
+    <t>I/II/III</t>
   </si>
   <si>
     <t>Theory</t>
@@ -1940,7 +1946,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2035,6 +2041,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2625,7 +2634,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.21875" customWidth="1"/>
@@ -2633,11 +2642,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="51" t="s">
-        <v>206</v>
-      </c>
-      <c r="B1" s="52" t="s">
-        <v>207</v>
+      <c r="A1" s="52" t="s">
+        <v>208</v>
+      </c>
+      <c r="B1" s="53" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.25">
@@ -2721,18 +2730,18 @@
       </c>
     </row>
     <row r="12" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A12" s="48" t="s">
-        <v>203</v>
-      </c>
-      <c r="B12" s="48">
+      <c r="A12" s="49" t="s">
+        <v>205</v>
+      </c>
+      <c r="B12" s="49">
         <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A13" s="49" t="s">
-        <v>204</v>
-      </c>
-      <c r="B13" s="50">
+      <c r="A13" s="50" t="s">
+        <v>206</v>
+      </c>
+      <c r="B13" s="51">
         <v>60</v>
       </c>
     </row>
@@ -2793,19 +2802,27 @@
       </c>
     </row>
     <row r="21" spans="1:2" ht="15" x14ac:dyDescent="0.25">
-      <c r="A21" s="44" t="s">
+      <c r="A21" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="45" t="s">
+      <c r="B21" s="46" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="46" t="s">
+      <c r="A22" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="47" t="s">
+      <c r="B22" s="48" t="s">
         <v>202</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B23" s="44" t="s">
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -2865,7 +2882,7 @@
         <v>27</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G1" s="19" t="s">
         <v>61</v>
@@ -2906,7 +2923,7 @@
         <v>65</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G2" s="20" t="s">
         <v>62</v>
@@ -2939,7 +2956,7 @@
         <v>65</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G3" s="20" t="s">
         <v>62</v>
@@ -2972,7 +2989,7 @@
         <v>65</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G4" s="20" t="s">
         <v>62</v>
@@ -3005,7 +3022,7 @@
         <v>65</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G5" s="20" t="s">
         <v>62</v>
@@ -3038,7 +3055,7 @@
         <v>65</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G6" s="20" t="s">
         <v>62</v>
@@ -3071,7 +3088,7 @@
         <v>65</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G7" s="20" t="s">
         <v>62</v>
@@ -3104,7 +3121,7 @@
         <v>65</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G8" s="20" t="s">
         <v>62</v>
@@ -3137,7 +3154,7 @@
         <v>65</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G9" s="20" t="s">
         <v>62</v>
@@ -3170,7 +3187,7 @@
         <v>65</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G10" s="20" t="s">
         <v>63</v>
@@ -3203,7 +3220,7 @@
         <v>65</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G11" s="20" t="s">
         <v>63</v>
@@ -3236,7 +3253,7 @@
         <v>66</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G12" s="20" t="s">
         <v>63</v>
@@ -3269,7 +3286,7 @@
         <v>66</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G13" s="20" t="s">
         <v>63</v>
@@ -3302,7 +3319,7 @@
         <v>66</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G14" s="20" t="s">
         <v>63</v>
@@ -3335,7 +3352,7 @@
         <v>66</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G15" s="20" t="s">
         <v>63</v>
@@ -3368,7 +3385,7 @@
         <v>66</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G16" s="20" t="s">
         <v>63</v>
@@ -3401,7 +3418,7 @@
         <v>66</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G17" s="20" t="s">
         <v>63</v>
@@ -3434,7 +3451,7 @@
         <v>66</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G18" s="20" t="s">
         <v>63</v>
@@ -3467,7 +3484,7 @@
         <v>66</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G19" s="20" t="s">
         <v>63</v>
@@ -3500,7 +3517,7 @@
         <v>66</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G20" s="20" t="s">
         <v>63</v>
@@ -3533,7 +3550,7 @@
         <v>66</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G21" s="20" t="s">
         <v>63</v>
@@ -3566,7 +3583,7 @@
         <v>66</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G22" s="20" t="s">
         <v>63</v>
@@ -3599,7 +3616,7 @@
         <v>66</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G23" s="20" t="s">
         <v>63</v>
@@ -3632,7 +3649,7 @@
         <v>67</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G24" s="20" t="s">
         <v>63</v>
@@ -3665,7 +3682,7 @@
         <v>67</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G25" s="20" t="s">
         <v>63</v>
@@ -3698,7 +3715,7 @@
         <v>67</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G26" s="20" t="s">
         <v>63</v>
@@ -3731,7 +3748,7 @@
         <v>67</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G27" s="20" t="s">
         <v>63</v>
@@ -3764,7 +3781,7 @@
         <v>67</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G28" s="20" t="s">
         <v>63</v>
@@ -3797,7 +3814,7 @@
         <v>66</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G29" s="20" t="s">
         <v>63</v>
@@ -3830,7 +3847,7 @@
         <v>67</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G30" s="20" t="s">
         <v>63</v>
@@ -3863,7 +3880,7 @@
         <v>67</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G31" s="20" t="s">
         <v>63</v>
@@ -3896,7 +3913,7 @@
         <v>66</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G32" s="20" t="s">
         <v>64</v>
@@ -3929,7 +3946,7 @@
         <v>67</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G33" s="20" t="s">
         <v>64</v>
@@ -3962,7 +3979,7 @@
         <v>66</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G34" s="20" t="s">
         <v>64</v>
@@ -3995,7 +4012,7 @@
         <v>66</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G35" s="20" t="s">
         <v>64</v>
@@ -4028,7 +4045,7 @@
         <v>67</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G36" s="20" t="s">
         <v>64</v>
@@ -4061,7 +4078,7 @@
         <v>67</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G37" s="20" t="s">
         <v>64</v>
@@ -4094,7 +4111,7 @@
         <v>66</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G38" s="20" t="s">
         <v>64</v>
@@ -4127,7 +4144,7 @@
         <v>65</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G39" s="20" t="s">
         <v>64</v>
@@ -4160,7 +4177,7 @@
         <v>65</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G40" s="22" t="s">
         <v>62</v>
@@ -4193,7 +4210,7 @@
         <v>65</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G41" s="22" t="s">
         <v>62</v>
@@ -4226,7 +4243,7 @@
         <v>65</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G42" s="22" t="s">
         <v>62</v>
@@ -4259,7 +4276,7 @@
         <v>65</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G43" s="22" t="s">
         <v>62</v>
@@ -4292,7 +4309,7 @@
         <v>65</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G44" s="22" t="s">
         <v>62</v>
@@ -4325,7 +4342,7 @@
         <v>65</v>
       </c>
       <c r="F45" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G45" s="22" t="s">
         <v>62</v>
@@ -4358,7 +4375,7 @@
         <v>65</v>
       </c>
       <c r="F46" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G46" s="22" t="s">
         <v>62</v>
@@ -4391,7 +4408,7 @@
         <v>66</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G47" s="22" t="s">
         <v>63</v>
@@ -4424,7 +4441,7 @@
         <v>66</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G48" s="22" t="s">
         <v>63</v>
@@ -4457,7 +4474,7 @@
         <v>66</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G49" s="22" t="s">
         <v>63</v>
@@ -4490,7 +4507,7 @@
         <v>66</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G50" s="22" t="s">
         <v>63</v>
@@ -4523,7 +4540,7 @@
         <v>66</v>
       </c>
       <c r="F51" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G51" s="22" t="s">
         <v>63</v>
@@ -4556,7 +4573,7 @@
         <v>66</v>
       </c>
       <c r="F52" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G52" s="22" t="s">
         <v>63</v>
@@ -4589,7 +4606,7 @@
         <v>66</v>
       </c>
       <c r="F53" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G53" s="22" t="s">
         <v>63</v>
@@ -4622,7 +4639,7 @@
         <v>66</v>
       </c>
       <c r="F54" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G54" s="22" t="s">
         <v>63</v>
@@ -4655,7 +4672,7 @@
         <v>66</v>
       </c>
       <c r="F55" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G55" s="22" t="s">
         <v>63</v>
@@ -4688,7 +4705,7 @@
         <v>67</v>
       </c>
       <c r="F56" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G56" s="22" t="s">
         <v>63</v>
@@ -4721,7 +4738,7 @@
         <v>67</v>
       </c>
       <c r="F57" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G57" s="22" t="s">
         <v>63</v>
@@ -4754,7 +4771,7 @@
         <v>67</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G58" s="22" t="s">
         <v>63</v>
@@ -4787,7 +4804,7 @@
         <v>67</v>
       </c>
       <c r="F59" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G59" s="22" t="s">
         <v>63</v>
@@ -4820,7 +4837,7 @@
         <v>67</v>
       </c>
       <c r="F60" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G60" s="22" t="s">
         <v>63</v>
@@ -4853,7 +4870,7 @@
         <v>67</v>
       </c>
       <c r="F61" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G61" s="22" t="s">
         <v>63</v>
@@ -4886,7 +4903,7 @@
         <v>67</v>
       </c>
       <c r="F62" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G62" s="22" t="s">
         <v>63</v>
@@ -4919,7 +4936,7 @@
         <v>67</v>
       </c>
       <c r="F63" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G63" s="22" t="s">
         <v>63</v>
@@ -4952,7 +4969,7 @@
         <v>67</v>
       </c>
       <c r="F64" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G64" s="22" t="s">
         <v>63</v>
@@ -4985,7 +5002,7 @@
         <v>67</v>
       </c>
       <c r="F65" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G65" s="22" t="s">
         <v>63</v>
@@ -5018,7 +5035,7 @@
         <v>66</v>
       </c>
       <c r="F66" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G66" s="22" t="s">
         <v>63</v>
@@ -5051,7 +5068,7 @@
         <v>66</v>
       </c>
       <c r="F67" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G67" s="22" t="s">
         <v>63</v>
@@ -5084,7 +5101,7 @@
         <v>66</v>
       </c>
       <c r="F68" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G68" s="22" t="s">
         <v>63</v>
@@ -5117,7 +5134,7 @@
         <v>67</v>
       </c>
       <c r="F69" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G69" s="22" t="s">
         <v>63</v>
@@ -5150,7 +5167,7 @@
         <v>65</v>
       </c>
       <c r="F70" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G70" s="22" t="s">
         <v>63</v>
@@ -5183,7 +5200,7 @@
         <v>66</v>
       </c>
       <c r="F71" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G71" s="22" t="s">
         <v>63</v>
@@ -5216,7 +5233,7 @@
         <v>65</v>
       </c>
       <c r="F72" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G72" s="22" t="s">
         <v>63</v>
@@ -5249,7 +5266,7 @@
         <v>66</v>
       </c>
       <c r="F73" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G73" s="22" t="s">
         <v>63</v>
@@ -5282,7 +5299,7 @@
         <v>65</v>
       </c>
       <c r="F74" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G74" s="22" t="s">
         <v>63</v>
@@ -5315,7 +5332,7 @@
         <v>65</v>
       </c>
       <c r="F75" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G75" s="22" t="s">
         <v>63</v>
@@ -5348,7 +5365,7 @@
         <v>66</v>
       </c>
       <c r="F76" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G76" s="22" t="s">
         <v>63</v>
@@ -5381,7 +5398,7 @@
         <v>66</v>
       </c>
       <c r="F77" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G77" s="22" t="s">
         <v>63</v>
@@ -5414,7 +5431,7 @@
         <v>67</v>
       </c>
       <c r="F78" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G78" s="22" t="s">
         <v>63</v>
@@ -5447,7 +5464,7 @@
         <v>65</v>
       </c>
       <c r="F79" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G79" s="23" t="s">
         <v>62</v>
@@ -5480,7 +5497,7 @@
         <v>65</v>
       </c>
       <c r="F80" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G80" s="23" t="s">
         <v>62</v>
@@ -5513,7 +5530,7 @@
         <v>65</v>
       </c>
       <c r="F81" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G81" s="23" t="s">
         <v>62</v>
@@ -5546,7 +5563,7 @@
         <v>65</v>
       </c>
       <c r="F82" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G82" s="23" t="s">
         <v>62</v>
@@ -5579,7 +5596,7 @@
         <v>65</v>
       </c>
       <c r="F83" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G83" s="23" t="s">
         <v>62</v>
@@ -5612,7 +5629,7 @@
         <v>65</v>
       </c>
       <c r="F84" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G84" s="23" t="s">
         <v>62</v>
@@ -5645,7 +5662,7 @@
         <v>65</v>
       </c>
       <c r="F85" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G85" s="23" t="s">
         <v>62</v>
@@ -5678,7 +5695,7 @@
         <v>66</v>
       </c>
       <c r="F86" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G86" s="36" t="s">
         <v>62</v>
@@ -5711,7 +5728,7 @@
         <v>66</v>
       </c>
       <c r="F87" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G87" s="23" t="s">
         <v>63</v>
@@ -5744,7 +5761,7 @@
         <v>66</v>
       </c>
       <c r="F88" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G88" s="23" t="s">
         <v>63</v>
@@ -5777,7 +5794,7 @@
         <v>66</v>
       </c>
       <c r="F89" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G89" s="23" t="s">
         <v>63</v>
@@ -5810,7 +5827,7 @@
         <v>66</v>
       </c>
       <c r="F90" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G90" s="23" t="s">
         <v>63</v>
@@ -5843,7 +5860,7 @@
         <v>67</v>
       </c>
       <c r="F91" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G91" s="23" t="s">
         <v>63</v>
@@ -5876,7 +5893,7 @@
         <v>66</v>
       </c>
       <c r="F92" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G92" s="23" t="s">
         <v>63</v>
@@ -5909,7 +5926,7 @@
         <v>66</v>
       </c>
       <c r="F93" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G93" s="23" t="s">
         <v>63</v>
@@ -5942,7 +5959,7 @@
         <v>66</v>
       </c>
       <c r="F94" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G94" s="23" t="s">
         <v>63</v>
@@ -5975,7 +5992,7 @@
         <v>66</v>
       </c>
       <c r="F95" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G95" s="23" t="s">
         <v>63</v>
@@ -6008,7 +6025,7 @@
         <v>66</v>
       </c>
       <c r="F96" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G96" s="23" t="s">
         <v>63</v>
@@ -6041,7 +6058,7 @@
         <v>66</v>
       </c>
       <c r="F97" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G97" s="23" t="s">
         <v>63</v>
@@ -6074,7 +6091,7 @@
         <v>67</v>
       </c>
       <c r="F98" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G98" s="23" t="s">
         <v>63</v>
@@ -6107,7 +6124,7 @@
         <v>67</v>
       </c>
       <c r="F99" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G99" s="23" t="s">
         <v>63</v>
@@ -6140,7 +6157,7 @@
         <v>67</v>
       </c>
       <c r="F100" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G100" s="23" t="s">
         <v>63</v>
@@ -6173,7 +6190,7 @@
         <v>67</v>
       </c>
       <c r="F101" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G101" s="23" t="s">
         <v>63</v>
@@ -6206,7 +6223,7 @@
         <v>67</v>
       </c>
       <c r="F102" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G102" s="23" t="s">
         <v>63</v>
@@ -6239,7 +6256,7 @@
         <v>67</v>
       </c>
       <c r="F103" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G103" s="23" t="s">
         <v>63</v>
@@ -6272,7 +6289,7 @@
         <v>67</v>
       </c>
       <c r="F104" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G104" s="23" t="s">
         <v>63</v>
@@ -6305,7 +6322,7 @@
         <v>67</v>
       </c>
       <c r="F105" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G105" s="23" t="s">
         <v>63</v>
@@ -6338,7 +6355,7 @@
         <v>67</v>
       </c>
       <c r="F106" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G106" s="23" t="s">
         <v>63</v>
@@ -6371,7 +6388,7 @@
         <v>67</v>
       </c>
       <c r="F107" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G107" s="23" t="s">
         <v>63</v>
@@ -6404,7 +6421,7 @@
         <v>67</v>
       </c>
       <c r="F108" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G108" s="23" t="s">
         <v>63</v>
@@ -6437,7 +6454,7 @@
         <v>65</v>
       </c>
       <c r="F109" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G109" s="23" t="s">
         <v>64</v>
@@ -6470,7 +6487,7 @@
         <v>67</v>
       </c>
       <c r="F110" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G110" s="23" t="s">
         <v>64</v>
@@ -6503,7 +6520,7 @@
         <v>67</v>
       </c>
       <c r="F111" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G111" s="23" t="s">
         <v>64</v>
@@ -6536,7 +6553,7 @@
         <v>67</v>
       </c>
       <c r="F112" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G112" s="23" t="s">
         <v>64</v>
@@ -6569,7 +6586,7 @@
         <v>67</v>
       </c>
       <c r="F113" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G113" s="23" t="s">
         <v>64</v>
@@ -6602,7 +6619,7 @@
         <v>66</v>
       </c>
       <c r="F114" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G114" s="23" t="s">
         <v>64</v>
@@ -6635,7 +6652,7 @@
         <v>66</v>
       </c>
       <c r="F115" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G115" s="23" t="s">
         <v>64</v>
@@ -6668,7 +6685,7 @@
         <v>66</v>
       </c>
       <c r="F116" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G116" s="23" t="s">
         <v>64</v>
@@ -6701,7 +6718,7 @@
         <v>66</v>
       </c>
       <c r="F117" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G117" s="22" t="s">
         <v>63</v>
@@ -6734,7 +6751,7 @@
         <v>66</v>
       </c>
       <c r="F118" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G118" s="22" t="s">
         <v>63</v>
@@ -6767,7 +6784,7 @@
         <v>66</v>
       </c>
       <c r="F119" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G119" s="22" t="s">
         <v>63</v>
@@ -6800,7 +6817,7 @@
         <v>65</v>
       </c>
       <c r="F120" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G120" s="22" t="s">
         <v>63</v>
@@ -6833,7 +6850,7 @@
         <v>65</v>
       </c>
       <c r="F121" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G121" s="22" t="s">
         <v>63</v>
@@ -6866,7 +6883,7 @@
         <v>65</v>
       </c>
       <c r="F122" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G122" s="22" t="s">
         <v>63</v>
@@ -6899,7 +6916,7 @@
         <v>65</v>
       </c>
       <c r="F123" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G123" s="22" t="s">
         <v>63</v>
@@ -6932,7 +6949,7 @@
         <v>67</v>
       </c>
       <c r="F124" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G124" s="22" t="s">
         <v>63</v>
@@ -6965,7 +6982,7 @@
         <v>66</v>
       </c>
       <c r="F125" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G125" s="22" t="s">
         <v>63</v>
@@ -6998,7 +7015,7 @@
         <v>66</v>
       </c>
       <c r="F126" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G126" s="22" t="s">
         <v>63</v>
@@ -7031,7 +7048,7 @@
         <v>66</v>
       </c>
       <c r="F127" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G127" s="22" t="s">
         <v>63</v>
@@ -7064,7 +7081,7 @@
         <v>66</v>
       </c>
       <c r="F128" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G128" s="22" t="s">
         <v>63</v>
@@ -7097,7 +7114,7 @@
         <v>66</v>
       </c>
       <c r="F129" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G129" s="22" t="s">
         <v>63</v>
@@ -7130,7 +7147,7 @@
         <v>67</v>
       </c>
       <c r="F130" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G130" s="22" t="s">
         <v>63</v>
@@ -7163,7 +7180,7 @@
         <v>66</v>
       </c>
       <c r="F131" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G131" s="22" t="s">
         <v>63</v>
@@ -7196,7 +7213,7 @@
         <v>67</v>
       </c>
       <c r="F132" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G132" s="22" t="s">
         <v>63</v>
@@ -7229,7 +7246,7 @@
         <v>67</v>
       </c>
       <c r="F133" s="12" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G133" s="22" t="s">
         <v>63</v>
@@ -7262,7 +7279,7 @@
         <v>67</v>
       </c>
       <c r="F134" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G134" s="22" t="s">
         <v>63</v>
@@ -7295,7 +7312,7 @@
         <v>67</v>
       </c>
       <c r="F135" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G135" s="22" t="s">
         <v>63</v>
@@ -7328,7 +7345,7 @@
         <v>67</v>
       </c>
       <c r="F136" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G136" s="22" t="s">
         <v>63</v>
@@ -7361,7 +7378,7 @@
         <v>66</v>
       </c>
       <c r="F137" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G137" s="22" t="s">
         <v>63</v>
@@ -7394,7 +7411,7 @@
         <v>67</v>
       </c>
       <c r="F138" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G138" s="22" t="s">
         <v>63</v>
@@ -7427,7 +7444,7 @@
         <v>67</v>
       </c>
       <c r="F139" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G139" s="22" t="s">
         <v>63</v>
@@ -7460,7 +7477,7 @@
         <v>67</v>
       </c>
       <c r="F140" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G140" s="22" t="s">
         <v>63</v>
@@ -7493,7 +7510,7 @@
         <v>67</v>
       </c>
       <c r="F141" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G141" s="22" t="s">
         <v>63</v>
@@ -7526,7 +7543,7 @@
         <v>67</v>
       </c>
       <c r="F142" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G142" s="22" t="s">
         <v>63</v>
@@ -7559,7 +7576,7 @@
         <v>66</v>
       </c>
       <c r="F143" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G143" s="22" t="s">
         <v>63</v>
@@ -7592,7 +7609,7 @@
         <v>67</v>
       </c>
       <c r="F144" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G144" s="22" t="s">
         <v>63</v>
@@ -7625,7 +7642,7 @@
         <v>66</v>
       </c>
       <c r="F145" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G145" s="22" t="s">
         <v>63</v>
@@ -7658,7 +7675,7 @@
         <v>66</v>
       </c>
       <c r="F146" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G146" s="22" t="s">
         <v>63</v>
@@ -7691,7 +7708,7 @@
         <v>66</v>
       </c>
       <c r="F147" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G147" s="22" t="s">
         <v>63</v>
@@ -7724,7 +7741,7 @@
         <v>65</v>
       </c>
       <c r="F148" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G148" s="22" t="s">
         <v>62</v>
@@ -7757,7 +7774,7 @@
         <v>65</v>
       </c>
       <c r="F149" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G149" s="22" t="s">
         <v>62</v>
@@ -7790,7 +7807,7 @@
         <v>65</v>
       </c>
       <c r="F150" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G150" s="22" t="s">
         <v>62</v>
@@ -7823,7 +7840,7 @@
         <v>65</v>
       </c>
       <c r="F151" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G151" s="22" t="s">
         <v>62</v>
@@ -7856,7 +7873,7 @@
         <v>65</v>
       </c>
       <c r="F152" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G152" s="22" t="s">
         <v>62</v>
@@ -7889,7 +7906,7 @@
         <v>65</v>
       </c>
       <c r="F153" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G153" s="22" t="s">
         <v>62</v>
